--- a/Arya_Temp/Cardio.xlsx
+++ b/Arya_Temp/Cardio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arsarya\Downloads\EXT\Arya_Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arsarya\Downloads\EXT\THE_A\Arya_Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89877A3-6B5D-4800-A1B1-300A7BD17CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FD1EDC-6F8B-4500-B8D6-1B3661ECF4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{0E5B9E36-B148-419A-94B9-5F003CA340C4}"/>
   </bookViews>
@@ -34,17 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>STAND</t>
   </si>
   <si>
-    <t>SIT</t>
-  </si>
-  <si>
-    <t>LYING</t>
-  </si>
-  <si>
     <t>9 to 3</t>
   </si>
   <si>
@@ -78,12 +72,6 @@
     <t>Twisters</t>
   </si>
   <si>
-    <t>Leg raise</t>
-  </si>
-  <si>
-    <t>Butterfly crunch</t>
-  </si>
-  <si>
     <t>Alt elbow knee tap</t>
   </si>
   <si>
@@ -99,23 +87,59 @@
     <t>Deep breaths</t>
   </si>
   <si>
-    <t>Push ups</t>
-  </si>
-  <si>
-    <t>Elbow up down plank</t>
-  </si>
-  <si>
     <t>Bridge</t>
   </si>
   <si>
     <t>Back rest</t>
+  </si>
+  <si>
+    <t>Leg lift arm reach</t>
+  </si>
+  <si>
+    <t>Jump twisters</t>
+  </si>
+  <si>
+    <t>Plank walks</t>
+  </si>
+  <si>
+    <t>Crunches</t>
+  </si>
+  <si>
+    <t>Leg raises</t>
+  </si>
+  <si>
+    <t>Reverse crunch</t>
+  </si>
+  <si>
+    <t>Cycling</t>
+  </si>
+  <si>
+    <t>SIT/ LIE</t>
+  </si>
+  <si>
+    <t>Overhead reach</t>
+  </si>
+  <si>
+    <t>Read leg lifts</t>
+  </si>
+  <si>
+    <t>Front lunges</t>
+  </si>
+  <si>
+    <t>Skipping</t>
+  </si>
+  <si>
+    <t>Sitted crunches</t>
+  </si>
+  <si>
+    <t>Triceps push-up</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +170,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -167,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -177,6 +208,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,148 +538,181 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B12" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D18" s="4"/>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D20" s="4"/>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D22" s="4"/>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D23" s="4"/>
     </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D24" s="4"/>
     </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D25" s="4"/>
     </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D26" s="4"/>
       <c r="E26" s="3"/>
     </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="D32" s="3"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.45">

--- a/Arya_Temp/Cardio.xlsx
+++ b/Arya_Temp/Cardio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arsarya\Downloads\EXT\THE_A\Arya_Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FD1EDC-6F8B-4500-B8D6-1B3661ECF4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A2FF68-C129-4F31-84E9-697E18D74C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{0E5B9E36-B148-419A-94B9-5F003CA340C4}"/>
   </bookViews>
@@ -120,9 +120,6 @@
     <t>Overhead reach</t>
   </si>
   <si>
-    <t>Read leg lifts</t>
-  </si>
-  <si>
     <t>Front lunges</t>
   </si>
   <si>
@@ -133,6 +130,9 @@
   </si>
   <si>
     <t>Triceps push-up</t>
+  </si>
+  <si>
+    <t>Rear leg lifts</t>
   </si>
 </sst>
 </file>
@@ -632,7 +632,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>21</v>
@@ -640,7 +640,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>1</v>
@@ -648,7 +648,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>17</v>
@@ -656,7 +656,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>25</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>18</v>
